--- a/ricevuta.xlsx
+++ b/ricevuta.xlsx
@@ -92,7 +92,7 @@
     <t xml:space="preserve">{{via}}</t>
   </si>
   <si>
-    <t xml:space="preserve">cap</t>
+    <t xml:space="preserve">Cap</t>
   </si>
   <si>
     <t xml:space="preserve">{{CAP}}</t>
